--- a/data/storage_change/Sacramento_Primary_spring_annual_storage_change_summary.xlsx
+++ b/data/storage_change/Sacramento_Primary_spring_annual_storage_change_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,31 +497,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1930</v>
+        <v>1950</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>-1661.006831938529</v>
+        <v>16934.00125234167</v>
       </c>
       <c r="F2" t="n">
-        <v>-1661.006831938529</v>
+        <v>-73754.25560375601</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>160378.1166116674</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>104088.6057984919</v>
       </c>
       <c r="I2" t="n">
-        <v>-1494.906148744676</v>
+        <v>-53018.75476235448</v>
       </c>
       <c r="J2" t="n">
-        <v>958.9827415455175</v>
+        <v>60791.19906429225</v>
       </c>
       <c r="K2" t="n">
-        <v>-1661.006831938529</v>
+        <v>16934.00125234167</v>
       </c>
     </row>
     <row r="3">
@@ -536,31 +536,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>-320855.6590007569</v>
+        <v>-389240.7042502491</v>
       </c>
       <c r="F3" t="n">
-        <v>-137906.0884621718</v>
+        <v>-222599.616139437</v>
       </c>
       <c r="G3" t="n">
-        <v>6743.195700162313</v>
+        <v>16968.46431429811</v>
       </c>
       <c r="H3" t="n">
-        <v>6695.859798949249</v>
+        <v>12127.64590302942</v>
       </c>
       <c r="I3" t="n">
-        <v>-129850.8961309304</v>
+        <v>-184850.0377185003</v>
       </c>
       <c r="J3" t="n">
-        <v>66560.75939382429</v>
+        <v>82931.24433476527</v>
       </c>
       <c r="K3" t="n">
-        <v>-322516.6658326954</v>
+        <v>-372306.7029979074</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>779194.660536029</v>
+        <v>1286405.967907131</v>
       </c>
       <c r="F4" t="n">
-        <v>-28335.07161486858</v>
+        <v>-66833.04587188159</v>
       </c>
       <c r="G4" t="n">
-        <v>667527.0330217039</v>
+        <v>970563.236241515</v>
       </c>
       <c r="H4" t="n">
-        <v>372643.3448185345</v>
+        <v>725546.9453306335</v>
       </c>
       <c r="I4" t="n">
-        <v>-25798.13485492828</v>
+        <v>-44285.92328010941</v>
       </c>
       <c r="J4" t="n">
-        <v>200476.4465648108</v>
+        <v>355265.1863294024</v>
       </c>
       <c r="K4" t="n">
-        <v>456677.9947033336</v>
+        <v>914099.2649092233</v>
       </c>
     </row>
     <row r="5">
@@ -614,31 +614,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>18418.62708235538</v>
+        <v>-628556.0406587964</v>
       </c>
       <c r="F5" t="n">
-        <v>-73754.25560375601</v>
+        <v>-250111.1090428115</v>
       </c>
       <c r="G5" t="n">
-        <v>160378.1166116674</v>
+        <v>21639.60690852935</v>
       </c>
       <c r="H5" t="n">
-        <v>104830.9187134987</v>
+        <v>17012.62470817218</v>
       </c>
       <c r="I5" t="n">
-        <v>-53018.75476235448</v>
+        <v>-121629.3593463585</v>
       </c>
       <c r="J5" t="n">
-        <v>60905.71327095896</v>
+        <v>54727.54631545868</v>
       </c>
       <c r="K5" t="n">
-        <v>475096.621785689</v>
+        <v>285543.2242504269</v>
       </c>
     </row>
     <row r="6">
@@ -653,31 +653,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1951</v>
+        <v>1954</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>-391710.7264495538</v>
+        <v>20340.27780851793</v>
       </c>
       <c r="F6" t="n">
-        <v>-223309.9346857556</v>
+        <v>-100630.8363743418</v>
       </c>
       <c r="G6" t="n">
-        <v>16968.46431429811</v>
+        <v>135699.1753031523</v>
       </c>
       <c r="H6" t="n">
-        <v>12127.64590302942</v>
+        <v>100683.524000564</v>
       </c>
       <c r="I6" t="n">
-        <v>-185875.1717968191</v>
+        <v>-76662.23501470783</v>
       </c>
       <c r="J6" t="n">
-        <v>83317.0453183967</v>
+        <v>49442.33412972634</v>
       </c>
       <c r="K6" t="n">
-        <v>83385.89533613517</v>
+        <v>305883.5020589448</v>
       </c>
     </row>
     <row r="7">
@@ -692,31 +692,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>1301582.143058382</v>
+        <v>-670784.4671303981</v>
       </c>
       <c r="F7" t="n">
-        <v>-66833.04587188159</v>
+        <v>-128801.7553016696</v>
       </c>
       <c r="G7" t="n">
-        <v>985739.4113927665</v>
+        <v>2542.467864065749</v>
       </c>
       <c r="H7" t="n">
-        <v>736170.2679365096</v>
+        <v>-621.9609563335971</v>
       </c>
       <c r="I7" t="n">
-        <v>-44285.92328010941</v>
+        <v>-96826.68006716194</v>
       </c>
       <c r="J7" t="n">
-        <v>360868.9707625076</v>
+        <v>35096.09375338657</v>
       </c>
       <c r="K7" t="n">
-        <v>1384968.038394517</v>
+        <v>-364900.9650714534</v>
       </c>
     </row>
     <row r="8">
@@ -731,31 +731,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1953</v>
+        <v>1956</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>-631324.9338764461</v>
+        <v>472360.4233718156</v>
       </c>
       <c r="F8" t="n">
-        <v>-250111.1090428115</v>
+        <v>-73754.25376603304</v>
       </c>
       <c r="G8" t="n">
-        <v>21639.60690852935</v>
+        <v>226294.4675660743</v>
       </c>
       <c r="H8" t="n">
-        <v>17012.62470817218</v>
+        <v>134814.8964655724</v>
       </c>
       <c r="I8" t="n">
-        <v>-122839.9069738909</v>
+        <v>-34933.37966444122</v>
       </c>
       <c r="J8" t="n">
-        <v>54884.0130794814</v>
+        <v>64425.14650827413</v>
       </c>
       <c r="K8" t="n">
-        <v>753643.1045180712</v>
+        <v>107459.4583003622</v>
       </c>
     </row>
     <row r="9">
@@ -770,31 +770,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>20524.44192321299</v>
+        <v>-272132.9990024692</v>
       </c>
       <c r="F9" t="n">
-        <v>-100630.8363743418</v>
+        <v>-159686.4337119934</v>
       </c>
       <c r="G9" t="n">
-        <v>135699.1753031523</v>
+        <v>137937.3448296039</v>
       </c>
       <c r="H9" t="n">
-        <v>100683.524000564</v>
+        <v>87591.08570313349</v>
       </c>
       <c r="I9" t="n">
-        <v>-76662.23501470783</v>
+        <v>-124951.7903048823</v>
       </c>
       <c r="J9" t="n">
-        <v>49453.94866083875</v>
+        <v>73214.23397443532</v>
       </c>
       <c r="K9" t="n">
-        <v>774167.5464412841</v>
+        <v>-164673.540702107</v>
       </c>
     </row>
     <row r="10">
@@ -809,31 +809,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1955</v>
+        <v>1958</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>-673423.6042363585</v>
+        <v>748285.033463008</v>
       </c>
       <c r="F10" t="n">
-        <v>-128801.7553016696</v>
+        <v>-18688.07760738932</v>
       </c>
       <c r="G10" t="n">
-        <v>2542.467864065749</v>
+        <v>238772.0283182746</v>
       </c>
       <c r="H10" t="n">
-        <v>-621.9609563335971</v>
+        <v>133622.2555331981</v>
       </c>
       <c r="I10" t="n">
-        <v>-96826.68006716194</v>
+        <v>-8624.119426747402</v>
       </c>
       <c r="J10" t="n">
-        <v>35264.34614327503</v>
+        <v>54600.75418882747</v>
       </c>
       <c r="K10" t="n">
-        <v>100743.9422049256</v>
+        <v>583611.492760901</v>
       </c>
     </row>
     <row r="11">
@@ -848,31 +848,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1956</v>
+        <v>1959</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
-        <v>473185.8745094438</v>
+        <v>-877178.1118039549</v>
       </c>
       <c r="F11" t="n">
-        <v>-73754.25376603304</v>
+        <v>-277244.4987423961</v>
       </c>
       <c r="G11" t="n">
-        <v>226294.4675660743</v>
+        <v>9111.460695208709</v>
       </c>
       <c r="H11" t="n">
-        <v>134814.8964655724</v>
+        <v>1019.209586931697</v>
       </c>
       <c r="I11" t="n">
-        <v>-34933.37966444122</v>
+        <v>-75859.78981197922</v>
       </c>
       <c r="J11" t="n">
-        <v>64419.32866832567</v>
+        <v>46017.78546521544</v>
       </c>
       <c r="K11" t="n">
-        <v>573929.8167143693</v>
+        <v>-293566.6190430539</v>
       </c>
     </row>
     <row r="12">
@@ -887,31 +887,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="E12" t="n">
-        <v>-272926.5208391009</v>
+        <v>-527289.9707215863</v>
       </c>
       <c r="F12" t="n">
-        <v>-161756.3751309727</v>
+        <v>-214805.7532435415</v>
       </c>
       <c r="G12" t="n">
-        <v>137937.3448296039</v>
+        <v>127033.4498997481</v>
       </c>
       <c r="H12" t="n">
-        <v>88356.93745254201</v>
+        <v>21958.17624659607</v>
       </c>
       <c r="I12" t="n">
-        <v>-125779.766872474</v>
+        <v>-62315.79182344802</v>
       </c>
       <c r="J12" t="n">
-        <v>73652.07465826665</v>
+        <v>41872.64877785408</v>
       </c>
       <c r="K12" t="n">
-        <v>301003.2958752684</v>
+        <v>-820856.5897646402</v>
       </c>
     </row>
     <row r="13">
@@ -926,31 +926,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E13" t="n">
-        <v>751721.834776629</v>
+        <v>-354778.6677234822</v>
       </c>
       <c r="F13" t="n">
-        <v>-18688.07760738932</v>
+        <v>-199133.5160590645</v>
       </c>
       <c r="G13" t="n">
-        <v>242110.6435101765</v>
+        <v>37181.7419988938</v>
       </c>
       <c r="H13" t="n">
-        <v>133622.2555331981</v>
+        <v>13510.67343683863</v>
       </c>
       <c r="I13" t="n">
-        <v>-8624.119426747402</v>
+        <v>-52667.47939629667</v>
       </c>
       <c r="J13" t="n">
-        <v>55096.91321662423</v>
+        <v>31891.70347597244</v>
       </c>
       <c r="K13" t="n">
-        <v>1052725.130651897</v>
+        <v>-1175635.257488122</v>
       </c>
     </row>
     <row r="14">
@@ -965,31 +965,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1959</v>
+        <v>1962</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>-880695.117140264</v>
+        <v>137535.9494739562</v>
       </c>
       <c r="F14" t="n">
-        <v>-277244.4987423961</v>
+        <v>-119037.96749917</v>
       </c>
       <c r="G14" t="n">
-        <v>9111.460695208709</v>
+        <v>294840.4897313155</v>
       </c>
       <c r="H14" t="n">
-        <v>1019.209586931697</v>
+        <v>19426.25896493952</v>
       </c>
       <c r="I14" t="n">
-        <v>-75859.78981197922</v>
+        <v>-24731.77517436429</v>
       </c>
       <c r="J14" t="n">
-        <v>46029.95473499597</v>
+        <v>45057.176872057</v>
       </c>
       <c r="K14" t="n">
-        <v>172030.0135116333</v>
+        <v>-1038099.308014166</v>
       </c>
     </row>
     <row r="15">
@@ -1004,31 +1004,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
-        <v>-536250.5529373842</v>
+        <v>-3442.649596121522</v>
       </c>
       <c r="F15" t="n">
-        <v>-214805.7532435415</v>
+        <v>-228154.6850941588</v>
       </c>
       <c r="G15" t="n">
-        <v>127033.4498997481</v>
+        <v>46477.17749861741</v>
       </c>
       <c r="H15" t="n">
-        <v>21958.17624659607</v>
+        <v>26961.41601862184</v>
       </c>
       <c r="I15" t="n">
-        <v>-65712.33514363292</v>
+        <v>-8783.355464536173</v>
       </c>
       <c r="J15" t="n">
-        <v>42137.60211907782</v>
+        <v>33266.22565483599</v>
       </c>
       <c r="K15" t="n">
-        <v>-364220.539425751</v>
+        <v>-1041541.957610288</v>
       </c>
     </row>
     <row r="16">
@@ -1043,31 +1043,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1961</v>
+        <v>1964</v>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
-        <v>-353074.5792101304</v>
+        <v>-313741.4031489881</v>
       </c>
       <c r="F16" t="n">
-        <v>-199133.5160590645</v>
+        <v>-56350.74755572519</v>
       </c>
       <c r="G16" t="n">
-        <v>37181.7419988938</v>
+        <v>22730.35563803582</v>
       </c>
       <c r="H16" t="n">
-        <v>14361.20006073523</v>
+        <v>7517.907082671267</v>
       </c>
       <c r="I16" t="n">
-        <v>-52667.47939629667</v>
+        <v>-30416.81557034437</v>
       </c>
       <c r="J16" t="n">
-        <v>31912.54178303752</v>
+        <v>12730.3108316115</v>
       </c>
       <c r="K16" t="n">
-        <v>-717295.1186358815</v>
+        <v>-1355283.360759276</v>
       </c>
     </row>
     <row r="17">
@@ -1082,31 +1082,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E17" t="n">
-        <v>139103.1990819699</v>
+        <v>-18069.50334199408</v>
       </c>
       <c r="F17" t="n">
-        <v>-119037.96749917</v>
+        <v>-76925.26590792027</v>
       </c>
       <c r="G17" t="n">
-        <v>294840.4897313155</v>
+        <v>49960.74993128868</v>
       </c>
       <c r="H17" t="n">
-        <v>19426.25896493952</v>
+        <v>18731.83761721326</v>
       </c>
       <c r="I17" t="n">
-        <v>-24731.77517436429</v>
+        <v>-13558.23594592888</v>
       </c>
       <c r="J17" t="n">
-        <v>45061.57363110612</v>
+        <v>17670.77714072189</v>
       </c>
       <c r="K17" t="n">
-        <v>-578191.9195539115</v>
+        <v>-1373352.86410127</v>
       </c>
     </row>
     <row r="18">
@@ -1121,31 +1121,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="E18" t="n">
-        <v>-2426.225174774136</v>
+        <v>119360.7559361238</v>
       </c>
       <c r="F18" t="n">
-        <v>-228154.6850941588</v>
+        <v>-35686.24995092046</v>
       </c>
       <c r="G18" t="n">
-        <v>46477.17749861741</v>
+        <v>64102.51996577727</v>
       </c>
       <c r="H18" t="n">
-        <v>26961.41601862184</v>
+        <v>28658.12002642064</v>
       </c>
       <c r="I18" t="n">
-        <v>-8783.355464536173</v>
+        <v>-12128.56126348264</v>
       </c>
       <c r="J18" t="n">
-        <v>33273.62984824614</v>
+        <v>14024.98820308427</v>
       </c>
       <c r="K18" t="n">
-        <v>-580618.1447286857</v>
+        <v>-1253992.108165146</v>
       </c>
     </row>
     <row r="19">
@@ -1160,31 +1160,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1964</v>
+        <v>1967</v>
       </c>
       <c r="D19" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="E19" t="n">
-        <v>-314295.8003509003</v>
+        <v>346809.0223768582</v>
       </c>
       <c r="F19" t="n">
-        <v>-56350.74755572519</v>
+        <v>-45540.93097240987</v>
       </c>
       <c r="G19" t="n">
-        <v>22730.35563803582</v>
+        <v>197982.323465581</v>
       </c>
       <c r="H19" t="n">
-        <v>7517.907082671267</v>
+        <v>18541.24201077025</v>
       </c>
       <c r="I19" t="n">
-        <v>-30416.81557034437</v>
+        <v>-9823.18913728259</v>
       </c>
       <c r="J19" t="n">
-        <v>12734.56328331865</v>
+        <v>24532.11326352293</v>
       </c>
       <c r="K19" t="n">
-        <v>-894913.945079586</v>
+        <v>-907183.0857882879</v>
       </c>
     </row>
     <row r="20">
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1965</v>
+        <v>1968</v>
       </c>
       <c r="D20" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="E20" t="n">
-        <v>-18191.71951238552</v>
+        <v>-42130.80162345593</v>
       </c>
       <c r="F20" t="n">
-        <v>-76925.26590792027</v>
+        <v>-114968.2816713443</v>
       </c>
       <c r="G20" t="n">
-        <v>49960.74993128868</v>
+        <v>21294.01878966502</v>
       </c>
       <c r="H20" t="n">
-        <v>18731.83761721326</v>
+        <v>13356.16042308738</v>
       </c>
       <c r="I20" t="n">
-        <v>-13558.23594592888</v>
+        <v>-12507.88258803019</v>
       </c>
       <c r="J20" t="n">
-        <v>17672.38941019135</v>
+        <v>14742.30341027926</v>
       </c>
       <c r="K20" t="n">
-        <v>-913105.6645919716</v>
+        <v>-949313.8874117439</v>
       </c>
     </row>
     <row r="21">
@@ -1238,31 +1238,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="D21" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E21" t="n">
-        <v>116677.0927120901</v>
+        <v>523608.4600320887</v>
       </c>
       <c r="F21" t="n">
-        <v>-35686.24995092046</v>
+        <v>-101288.2642500754</v>
       </c>
       <c r="G21" t="n">
-        <v>64102.51996577727</v>
+        <v>57276.85462749514</v>
       </c>
       <c r="H21" t="n">
-        <v>28658.12002642064</v>
+        <v>30599.51756716174</v>
       </c>
       <c r="I21" t="n">
-        <v>-12128.56126348264</v>
+        <v>-3269.50008480131</v>
       </c>
       <c r="J21" t="n">
-        <v>14112.4246017221</v>
+        <v>17103.69137059659</v>
       </c>
       <c r="K21" t="n">
-        <v>-796428.5718798814</v>
+        <v>-425705.4273796552</v>
       </c>
     </row>
     <row r="22">
@@ -1277,31 +1277,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1967</v>
+        <v>1970</v>
       </c>
       <c r="D22" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E22" t="n">
-        <v>349466.3801204428</v>
+        <v>9161.861639998344</v>
       </c>
       <c r="F22" t="n">
-        <v>-45540.93097240987</v>
+        <v>-37366.00803498815</v>
       </c>
       <c r="G22" t="n">
-        <v>197982.323465581</v>
+        <v>109641.9355284321</v>
       </c>
       <c r="H22" t="n">
-        <v>18676.15318382588</v>
+        <v>8084.650357840273</v>
       </c>
       <c r="I22" t="n">
-        <v>-9823.18913728259</v>
+        <v>-8531.338001088377</v>
       </c>
       <c r="J22" t="n">
-        <v>24566.64644161123</v>
+        <v>14234.73358490556</v>
       </c>
       <c r="K22" t="n">
-        <v>-446962.1917594386</v>
+        <v>-416543.5657396569</v>
       </c>
     </row>
     <row r="23">
@@ -1316,31 +1316,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="D23" t="n">
         <v>81</v>
       </c>
       <c r="E23" t="n">
-        <v>-43948.22758370911</v>
+        <v>-545973.5712598469</v>
       </c>
       <c r="F23" t="n">
-        <v>-114968.2816713443</v>
+        <v>-44839.20964198578</v>
       </c>
       <c r="G23" t="n">
-        <v>21724.48716690127</v>
+        <v>13606.71376762526</v>
       </c>
       <c r="H23" t="n">
-        <v>13356.16042308738</v>
+        <v>1742.024706392167</v>
       </c>
       <c r="I23" t="n">
-        <v>-12768.10820564278</v>
+        <v>-31269.70647007537</v>
       </c>
       <c r="J23" t="n">
-        <v>14795.56025398033</v>
+        <v>10665.45405439116</v>
       </c>
       <c r="K23" t="n">
-        <v>-490910.4193431477</v>
+        <v>-962517.1369995037</v>
       </c>
     </row>
     <row r="24">
@@ -1355,31 +1355,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="D24" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E24" t="n">
-        <v>528008.8530735205</v>
+        <v>-558735.8610922327</v>
       </c>
       <c r="F24" t="n">
-        <v>-101288.2642500754</v>
+        <v>-49545.71635920861</v>
       </c>
       <c r="G24" t="n">
-        <v>57276.85462749514</v>
+        <v>22166.49838558781</v>
       </c>
       <c r="H24" t="n">
-        <v>30945.5352263856</v>
+        <v>7014.255649565414</v>
       </c>
       <c r="I24" t="n">
-        <v>-3269.50008480131</v>
+        <v>-35173.85431963477</v>
       </c>
       <c r="J24" t="n">
-        <v>17222.11544716963</v>
+        <v>12221.60258298221</v>
       </c>
       <c r="K24" t="n">
-        <v>37098.43373037275</v>
+        <v>-1521252.998091736</v>
       </c>
     </row>
     <row r="25">
@@ -1394,31 +1394,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="D25" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E25" t="n">
-        <v>9587.174124659636</v>
+        <v>1197185.546993945</v>
       </c>
       <c r="F25" t="n">
-        <v>-37366.00803498815</v>
+        <v>-4001.360799699063</v>
       </c>
       <c r="G25" t="n">
-        <v>109641.9355284321</v>
+        <v>131827.3846030428</v>
       </c>
       <c r="H25" t="n">
-        <v>8084.650357840273</v>
+        <v>54631.9846846711</v>
       </c>
       <c r="I25" t="n">
-        <v>-8694.915984438156</v>
+        <v>-512.9112665122478</v>
       </c>
       <c r="J25" t="n">
-        <v>14241.11489217956</v>
+        <v>21464.39207771246</v>
       </c>
       <c r="K25" t="n">
-        <v>46685.60785503239</v>
+        <v>-324067.4510977911</v>
       </c>
     </row>
     <row r="26">
@@ -1433,31 +1433,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="D26" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E26" t="n">
-        <v>-549686.6759569097</v>
+        <v>-95745.09102471681</v>
       </c>
       <c r="F26" t="n">
-        <v>-44839.20964198578</v>
+        <v>-30227.38292107291</v>
       </c>
       <c r="G26" t="n">
-        <v>13606.71376762526</v>
+        <v>36358.54797222999</v>
       </c>
       <c r="H26" t="n">
-        <v>1742.024706392167</v>
+        <v>9379.329380894458</v>
       </c>
       <c r="I26" t="n">
-        <v>-31920.27051410684</v>
+        <v>-13422.5800997726</v>
       </c>
       <c r="J26" t="n">
-        <v>10782.27223424997</v>
+        <v>8650.512065620946</v>
       </c>
       <c r="K26" t="n">
-        <v>-503001.0681018773</v>
+        <v>-419812.5421225079</v>
       </c>
     </row>
     <row r="27">
@@ -1472,31 +1472,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1972</v>
+        <v>1975</v>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="E27" t="n">
-        <v>-559208.7940177863</v>
+        <v>88869.67782558189</v>
       </c>
       <c r="F27" t="n">
-        <v>-49545.71635920861</v>
+        <v>-29934.77028877555</v>
       </c>
       <c r="G27" t="n">
-        <v>22166.49838558781</v>
+        <v>42048.62711928642</v>
       </c>
       <c r="H27" t="n">
-        <v>7014.255649565414</v>
+        <v>10378.03149200756</v>
       </c>
       <c r="I27" t="n">
-        <v>-35874.29494037533</v>
+        <v>-8134.148677779457</v>
       </c>
       <c r="J27" t="n">
-        <v>12258.72409274468</v>
+        <v>7000.091634091486</v>
       </c>
       <c r="K27" t="n">
-        <v>-1062209.862119664</v>
+        <v>-330942.864296926</v>
       </c>
     </row>
     <row r="28">
@@ -1511,31 +1511,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1973</v>
+        <v>1976</v>
       </c>
       <c r="D28" t="n">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="E28" t="n">
-        <v>1200665.36694957</v>
+        <v>-1593267.9601351</v>
       </c>
       <c r="F28" t="n">
-        <v>-4001.360799699063</v>
+        <v>-111114.3359159424</v>
       </c>
       <c r="G28" t="n">
-        <v>131827.3846030428</v>
+        <v>20511.28208041157</v>
       </c>
       <c r="H28" t="n">
-        <v>54631.9846846711</v>
+        <v>-424.8847467792821</v>
       </c>
       <c r="I28" t="n">
-        <v>-512.9112665122478</v>
+        <v>-42629.56747744547</v>
       </c>
       <c r="J28" t="n">
-        <v>21541.08992183977</v>
+        <v>17362.3204238779</v>
       </c>
       <c r="K28" t="n">
-        <v>138455.5048299062</v>
+        <v>-1924210.824432026</v>
       </c>
     </row>
     <row r="29">
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1974</v>
+        <v>1977</v>
       </c>
       <c r="D29" t="n">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="E29" t="n">
-        <v>-96170.14662639485</v>
+        <v>-854557.9227865502</v>
       </c>
       <c r="F29" t="n">
-        <v>-30856.26149697001</v>
+        <v>-77566.90672914257</v>
       </c>
       <c r="G29" t="n">
-        <v>36358.54797222999</v>
+        <v>24461.6662032978</v>
       </c>
       <c r="H29" t="n">
-        <v>9379.329380894458</v>
+        <v>3217.441965362827</v>
       </c>
       <c r="I29" t="n">
-        <v>-13422.5800997726</v>
+        <v>-34965.36459602429</v>
       </c>
       <c r="J29" t="n">
-        <v>8682.001263880476</v>
+        <v>13337.41255369392</v>
       </c>
       <c r="K29" t="n">
-        <v>42285.35820351131</v>
+        <v>-2778768.747218576</v>
       </c>
     </row>
     <row r="30">
@@ -1589,31 +1589,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="D30" t="n">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="E30" t="n">
-        <v>88637.58865498131</v>
+        <v>1851729.302950135</v>
       </c>
       <c r="F30" t="n">
-        <v>-29934.77028877555</v>
+        <v>-14279.16185686472</v>
       </c>
       <c r="G30" t="n">
-        <v>42048.62711928642</v>
+        <v>103897.1860099822</v>
       </c>
       <c r="H30" t="n">
-        <v>10378.03149200756</v>
+        <v>55035.18068666118</v>
       </c>
       <c r="I30" t="n">
-        <v>-8134.148677779457</v>
+        <v>-2585.533581155486</v>
       </c>
       <c r="J30" t="n">
-        <v>7002.288441746041</v>
+        <v>20893.91163983454</v>
       </c>
       <c r="K30" t="n">
-        <v>130922.9468584926</v>
+        <v>-927039.4442684408</v>
       </c>
     </row>
     <row r="31">
@@ -1628,31 +1628,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="D31" t="n">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="E31" t="n">
-        <v>-1599218.718523697</v>
+        <v>-98851.76543164854</v>
       </c>
       <c r="F31" t="n">
-        <v>-111114.3359159424</v>
+        <v>-38276.88946146256</v>
       </c>
       <c r="G31" t="n">
-        <v>20511.28208041157</v>
+        <v>12817.30391536475</v>
       </c>
       <c r="H31" t="n">
-        <v>-424.8847467792821</v>
+        <v>9295.975668198902</v>
       </c>
       <c r="I31" t="n">
-        <v>-42629.56747744547</v>
+        <v>-12278.12258346646</v>
       </c>
       <c r="J31" t="n">
-        <v>17445.82991247313</v>
+        <v>7031.000243109105</v>
       </c>
       <c r="K31" t="n">
-        <v>-1468295.771665205</v>
+        <v>-1025891.209700089</v>
       </c>
     </row>
     <row r="32">
@@ -1667,31 +1667,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="D32" t="n">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="E32" t="n">
-        <v>-853769.5708570665</v>
+        <v>650720.5316320966</v>
       </c>
       <c r="F32" t="n">
-        <v>-77566.90672914257</v>
+        <v>-7724.847660695348</v>
       </c>
       <c r="G32" t="n">
-        <v>26252.51915940839</v>
+        <v>28854.88590171794</v>
       </c>
       <c r="H32" t="n">
-        <v>3217.441965362827</v>
+        <v>14812.14592474862</v>
       </c>
       <c r="I32" t="n">
-        <v>-34965.36459602429</v>
+        <v>-1496.092049327094</v>
       </c>
       <c r="J32" t="n">
-        <v>13377.48717842466</v>
+        <v>5848.616516560788</v>
       </c>
       <c r="K32" t="n">
-        <v>-2322065.342522271</v>
+        <v>-375170.6780679928</v>
       </c>
     </row>
     <row r="33">
@@ -1706,31 +1706,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="D33" t="n">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="E33" t="n">
-        <v>1855732.931820001</v>
+        <v>-426862.0581862632</v>
       </c>
       <c r="F33" t="n">
-        <v>-14279.16185686472</v>
+        <v>-66290.46929392013</v>
       </c>
       <c r="G33" t="n">
-        <v>103897.1860099822</v>
+        <v>14478.45956254507</v>
       </c>
       <c r="H33" t="n">
-        <v>55035.18068666118</v>
+        <v>4144.45039120031</v>
       </c>
       <c r="I33" t="n">
-        <v>-2585.533581155486</v>
+        <v>-15133.71507046019</v>
       </c>
       <c r="J33" t="n">
-        <v>20918.45164937842</v>
+        <v>7647.722987202901</v>
       </c>
       <c r="K33" t="n">
-        <v>-466332.4107022705</v>
+        <v>-802032.736254256</v>
       </c>
     </row>
     <row r="34">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="D34" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E34" t="n">
-        <v>-100577.0887024071</v>
+        <v>857814.4299076151</v>
       </c>
       <c r="F34" t="n">
-        <v>-38276.88946146256</v>
+        <v>-14826.26378822175</v>
       </c>
       <c r="G34" t="n">
-        <v>12817.30391536475</v>
+        <v>90724.60144092393</v>
       </c>
       <c r="H34" t="n">
-        <v>9295.975668198902</v>
+        <v>19078.32246185589</v>
       </c>
       <c r="I34" t="n">
-        <v>-12278.12258346646</v>
+        <v>-173.8834726068164</v>
       </c>
       <c r="J34" t="n">
-        <v>7047.6933421401</v>
+        <v>9488.96506745795</v>
       </c>
       <c r="K34" t="n">
-        <v>-566909.4994046775</v>
+        <v>55781.69365335908</v>
       </c>
     </row>
     <row r="35">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="D35" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E35" t="n">
-        <v>652550.251982757</v>
+        <v>1099951.698839163</v>
       </c>
       <c r="F35" t="n">
-        <v>-7724.847660695348</v>
+        <v>-9038.64258036409</v>
       </c>
       <c r="G35" t="n">
-        <v>28854.88590171794</v>
+        <v>51650.19504922262</v>
       </c>
       <c r="H35" t="n">
-        <v>14812.14592474862</v>
+        <v>21391.25299449445</v>
       </c>
       <c r="I35" t="n">
-        <v>-1496.092049327094</v>
+        <v>455.5834051721066</v>
       </c>
       <c r="J35" t="n">
-        <v>5888.957111013757</v>
+        <v>8064.534866606284</v>
       </c>
       <c r="K35" t="n">
-        <v>85640.75257807947</v>
+        <v>1155733.392492522</v>
       </c>
     </row>
     <row r="36">
@@ -1823,31 +1823,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1981</v>
+        <v>1984</v>
       </c>
       <c r="D36" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E36" t="n">
-        <v>-428645.821624121</v>
+        <v>-515705.8651728164</v>
       </c>
       <c r="F36" t="n">
-        <v>-66290.46929392013</v>
+        <v>-52460.07146637129</v>
       </c>
       <c r="G36" t="n">
-        <v>14478.45956254507</v>
+        <v>17370.76407221303</v>
       </c>
       <c r="H36" t="n">
-        <v>4144.45039120031</v>
+        <v>6091.402807642075</v>
       </c>
       <c r="I36" t="n">
-        <v>-15133.71507046019</v>
+        <v>-18537.35731347238</v>
       </c>
       <c r="J36" t="n">
-        <v>7678.702442983431</v>
+        <v>9325.597750333382</v>
       </c>
       <c r="K36" t="n">
-        <v>-343005.0690460416</v>
+        <v>640027.527319706</v>
       </c>
     </row>
     <row r="37">
@@ -1862,31 +1862,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="D37" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E37" t="n">
-        <v>860537.1345390178</v>
+        <v>-679590.5676085823</v>
       </c>
       <c r="F37" t="n">
-        <v>-14826.26378822175</v>
+        <v>-34131.71088163059</v>
       </c>
       <c r="G37" t="n">
-        <v>90724.60144092393</v>
+        <v>4882.450151738301</v>
       </c>
       <c r="H37" t="n">
-        <v>19078.32246185589</v>
+        <v>2160.621958281749</v>
       </c>
       <c r="I37" t="n">
-        <v>-173.8834726068164</v>
+        <v>-17979.79468985494</v>
       </c>
       <c r="J37" t="n">
-        <v>9507.121792465972</v>
+        <v>6542.620133986143</v>
       </c>
       <c r="K37" t="n">
-        <v>517532.0654929762</v>
+        <v>-39563.04028887628</v>
       </c>
     </row>
     <row r="38">
@@ -1901,31 +1901,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="D38" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E38" t="n">
-        <v>1098450.671645133</v>
+        <v>971202.1032695196</v>
       </c>
       <c r="F38" t="n">
-        <v>-11762.7819218838</v>
+        <v>-11387.06391597674</v>
       </c>
       <c r="G38" t="n">
-        <v>51650.19504922262</v>
+        <v>73342.64687837972</v>
       </c>
       <c r="H38" t="n">
-        <v>21391.25299449445</v>
+        <v>23290.76069523347</v>
       </c>
       <c r="I38" t="n">
-        <v>455.5834051721066</v>
+        <v>-175.5181010412171</v>
       </c>
       <c r="J38" t="n">
-        <v>8110.216930570863</v>
+        <v>10170.85126599122</v>
       </c>
       <c r="K38" t="n">
-        <v>1615982.73713811</v>
+        <v>931639.0629806434</v>
       </c>
     </row>
     <row r="39">
@@ -1940,31 +1940,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="D39" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E39" t="n">
-        <v>-513764.566744263</v>
+        <v>-848463.2808872138</v>
       </c>
       <c r="F39" t="n">
-        <v>-52460.07146637129</v>
+        <v>-51148.77855563934</v>
       </c>
       <c r="G39" t="n">
-        <v>17370.76407221303</v>
+        <v>14104.35516891917</v>
       </c>
       <c r="H39" t="n">
-        <v>6091.402807642075</v>
+        <v>2139.574168487035</v>
       </c>
       <c r="I39" t="n">
-        <v>-18584.98544661866</v>
+        <v>-24951.99953325997</v>
       </c>
       <c r="J39" t="n">
-        <v>9375.22735670944</v>
+        <v>9416.883862361579</v>
       </c>
       <c r="K39" t="n">
-        <v>1102218.170393846</v>
+        <v>83175.78209342959</v>
       </c>
     </row>
     <row r="40">
@@ -1979,31 +1979,31 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="D40" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E40" t="n">
-        <v>-684375.3651891346</v>
+        <v>-188680.0569143353</v>
       </c>
       <c r="F40" t="n">
-        <v>-36638.35294075053</v>
+        <v>-37527.19441602936</v>
       </c>
       <c r="G40" t="n">
-        <v>4882.450151738301</v>
+        <v>56590.38621115501</v>
       </c>
       <c r="H40" t="n">
-        <v>2160.621958281749</v>
+        <v>7531.436233604154</v>
       </c>
       <c r="I40" t="n">
-        <v>-17979.79468985494</v>
+        <v>-14845.5028779269</v>
       </c>
       <c r="J40" t="n">
-        <v>6656.399880586474</v>
+        <v>7830.04085861205</v>
       </c>
       <c r="K40" t="n">
-        <v>417842.8052047119</v>
+        <v>-105504.2748209057</v>
       </c>
     </row>
     <row r="41">
@@ -2018,31 +2018,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="D41" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E41" t="n">
-        <v>972644.9530344603</v>
+        <v>-126083.2879306614</v>
       </c>
       <c r="F41" t="n">
-        <v>-12222.6112690167</v>
+        <v>-35951.06000917088</v>
       </c>
       <c r="G41" t="n">
-        <v>73342.64687837972</v>
+        <v>66748.60601151791</v>
       </c>
       <c r="H41" t="n">
-        <v>23290.76069523347</v>
+        <v>8648.207259322846</v>
       </c>
       <c r="I41" t="n">
-        <v>-175.5181010412171</v>
+        <v>-8573.597148957935</v>
       </c>
       <c r="J41" t="n">
-        <v>10201.46339701838</v>
+        <v>8818.172907143058</v>
       </c>
       <c r="K41" t="n">
-        <v>1390487.758239172</v>
+        <v>-231587.5627515671</v>
       </c>
     </row>
     <row r="42">
@@ -2057,31 +2057,31 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="D42" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E42" t="n">
-        <v>-849543.5488772506</v>
+        <v>-152570.8402891491</v>
       </c>
       <c r="F42" t="n">
-        <v>-51148.77855563934</v>
+        <v>-36327.49841624091</v>
       </c>
       <c r="G42" t="n">
-        <v>14104.35516891917</v>
+        <v>29222.71261182439</v>
       </c>
       <c r="H42" t="n">
-        <v>2139.574168487035</v>
+        <v>5981.929615631073</v>
       </c>
       <c r="I42" t="n">
-        <v>-24951.99953325997</v>
+        <v>-9825.772483110686</v>
       </c>
       <c r="J42" t="n">
-        <v>9444.953471857645</v>
+        <v>6222.903082903618</v>
       </c>
       <c r="K42" t="n">
-        <v>540944.2093619215</v>
+        <v>-384158.4030407163</v>
       </c>
     </row>
     <row r="43">
@@ -2096,31 +2096,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="D43" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E43" t="n">
-        <v>-190568.4215640542</v>
+        <v>-760423.3187291129</v>
       </c>
       <c r="F43" t="n">
-        <v>-37527.19441602936</v>
+        <v>-58367.45781590792</v>
       </c>
       <c r="G43" t="n">
-        <v>56590.38621115501</v>
+        <v>26007.10754407899</v>
       </c>
       <c r="H43" t="n">
-        <v>7531.436233604154</v>
+        <v>3975.161578009881</v>
       </c>
       <c r="I43" t="n">
-        <v>-14845.5028779269</v>
+        <v>-20408.69910014542</v>
       </c>
       <c r="J43" t="n">
-        <v>7856.278132284964</v>
+        <v>10726.27024890526</v>
       </c>
       <c r="K43" t="n">
-        <v>350375.7877978674</v>
+        <v>-1144581.721769829</v>
       </c>
     </row>
     <row r="44">
@@ -2135,31 +2135,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1989</v>
+        <v>1992</v>
       </c>
       <c r="D44" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E44" t="n">
-        <v>-123543.276036908</v>
+        <v>628019.3845531492</v>
       </c>
       <c r="F44" t="n">
-        <v>-35951.06000917088</v>
+        <v>-24435.75181405391</v>
       </c>
       <c r="G44" t="n">
-        <v>66748.60601151791</v>
+        <v>180589.8769694237</v>
       </c>
       <c r="H44" t="n">
-        <v>8648.207259322846</v>
+        <v>26813.37578265315</v>
       </c>
       <c r="I44" t="n">
-        <v>-8573.597148957935</v>
+        <v>-5587.043129432981</v>
       </c>
       <c r="J44" t="n">
-        <v>8889.11367084556</v>
+        <v>17481.79768941551</v>
       </c>
       <c r="K44" t="n">
-        <v>226832.5117609594</v>
+        <v>-516562.3372166801</v>
       </c>
     </row>
     <row r="45">
@@ -2174,31 +2174,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="D45" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E45" t="n">
-        <v>-154945.8937573455</v>
+        <v>891392.6860288909</v>
       </c>
       <c r="F45" t="n">
-        <v>-36327.49841624091</v>
+        <v>-10466.59864337382</v>
       </c>
       <c r="G45" t="n">
-        <v>29222.71261182439</v>
+        <v>148521.9610756969</v>
       </c>
       <c r="H45" t="n">
-        <v>5986.700198147193</v>
+        <v>22324.80374306585</v>
       </c>
       <c r="I45" t="n">
-        <v>-9825.772483110686</v>
+        <v>-2633.857168759304</v>
       </c>
       <c r="J45" t="n">
-        <v>6314.047093665887</v>
+        <v>14011.14771934416</v>
       </c>
       <c r="K45" t="n">
-        <v>71886.61800361387</v>
+        <v>374830.3488122108</v>
       </c>
     </row>
     <row r="46">
@@ -2213,31 +2213,31 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1991</v>
+        <v>1994</v>
       </c>
       <c r="D46" t="n">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="E46" t="n">
-        <v>-763092.7184996856</v>
+        <v>-460894.7089252512</v>
       </c>
       <c r="F46" t="n">
-        <v>-58367.45781590792</v>
+        <v>-49170.15647058181</v>
       </c>
       <c r="G46" t="n">
-        <v>26007.10754407899</v>
+        <v>17737.03319430811</v>
       </c>
       <c r="H46" t="n">
-        <v>3975.161578009881</v>
+        <v>4052.446429378165</v>
       </c>
       <c r="I46" t="n">
-        <v>-20408.69910014542</v>
+        <v>-13828.03771514078</v>
       </c>
       <c r="J46" t="n">
-        <v>10737.91404857313</v>
+        <v>6346.018417126812</v>
       </c>
       <c r="K46" t="n">
-        <v>-691206.1004960717</v>
+        <v>-86064.36011304037</v>
       </c>
     </row>
     <row r="47">
@@ -2252,31 +2252,31 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="D47" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="E47" t="n">
-        <v>631663.8798832336</v>
+        <v>1083567.383386916</v>
       </c>
       <c r="F47" t="n">
-        <v>-24435.75181405391</v>
+        <v>-24709.49060639631</v>
       </c>
       <c r="G47" t="n">
-        <v>180589.8769694237</v>
+        <v>129890.3023869569</v>
       </c>
       <c r="H47" t="n">
-        <v>26813.37578265315</v>
+        <v>22886.11931903459</v>
       </c>
       <c r="I47" t="n">
-        <v>-5587.043129432981</v>
+        <v>-1543.185334386943</v>
       </c>
       <c r="J47" t="n">
-        <v>17500.53099880302</v>
+        <v>12859.54594978048</v>
       </c>
       <c r="K47" t="n">
-        <v>-59542.22061283817</v>
+        <v>997503.0232738752</v>
       </c>
     </row>
     <row r="48">
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="D48" t="n">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="E48" t="n">
-        <v>900159.3420831311</v>
+        <v>-8733.415427881468</v>
       </c>
       <c r="F48" t="n">
-        <v>-10466.59864337382</v>
+        <v>-33163.20140950708</v>
       </c>
       <c r="G48" t="n">
-        <v>151587.0061221641</v>
+        <v>15294.75083070467</v>
       </c>
       <c r="H48" t="n">
-        <v>23172.58934827214</v>
+        <v>8197.968184077647</v>
       </c>
       <c r="I48" t="n">
-        <v>-2633.857168759304</v>
+        <v>-5601.824871180671</v>
       </c>
       <c r="J48" t="n">
-        <v>14271.03269020967</v>
+        <v>5585.291181613366</v>
       </c>
       <c r="K48" t="n">
-        <v>840617.1214702929</v>
+        <v>988769.6078459937</v>
       </c>
     </row>
     <row r="49">
@@ -2330,31 +2330,31 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1994</v>
+        <v>1997</v>
       </c>
       <c r="D49" t="n">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="E49" t="n">
-        <v>-462769.5437465803</v>
+        <v>-304812.3338927337</v>
       </c>
       <c r="F49" t="n">
-        <v>-49170.15647058181</v>
+        <v>-38072.80732296747</v>
       </c>
       <c r="G49" t="n">
-        <v>17737.03319430811</v>
+        <v>28597.20803161</v>
       </c>
       <c r="H49" t="n">
-        <v>4052.446429378165</v>
+        <v>3134.584874412747</v>
       </c>
       <c r="I49" t="n">
-        <v>-13828.03771514078</v>
+        <v>-11570.67477498793</v>
       </c>
       <c r="J49" t="n">
-        <v>6356.464499427103</v>
+        <v>6905.516686578169</v>
       </c>
       <c r="K49" t="n">
-        <v>377847.5777237126</v>
+        <v>683957.2739532599</v>
       </c>
     </row>
     <row r="50">
@@ -2369,31 +2369,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="D50" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="E50" t="n">
-        <v>1082071.013497181</v>
+        <v>843532.3847861905</v>
       </c>
       <c r="F50" t="n">
-        <v>-29083.61226058076</v>
+        <v>-35891.76467357231</v>
       </c>
       <c r="G50" t="n">
-        <v>129890.3023869569</v>
+        <v>44827.67402699932</v>
       </c>
       <c r="H50" t="n">
-        <v>23479.45523222402</v>
+        <v>18428.3261234367</v>
       </c>
       <c r="I50" t="n">
-        <v>-1543.185334386943</v>
+        <v>-307.9320221484953</v>
       </c>
       <c r="J50" t="n">
-        <v>12946.38810903571</v>
+        <v>7776.602479468377</v>
       </c>
       <c r="K50" t="n">
-        <v>1459918.591220894</v>
+        <v>1527489.65873945</v>
       </c>
     </row>
     <row r="51">
@@ -2408,31 +2408,31 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="D51" t="n">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="E51" t="n">
-        <v>-10876.6620881038</v>
+        <v>-668679.344600752</v>
       </c>
       <c r="F51" t="n">
-        <v>-33163.20140950708</v>
+        <v>-73805.54731452065</v>
       </c>
       <c r="G51" t="n">
-        <v>15294.75083070467</v>
+        <v>44013.2588697821</v>
       </c>
       <c r="H51" t="n">
-        <v>8197.968184077647</v>
+        <v>3344.369109869091</v>
       </c>
       <c r="I51" t="n">
-        <v>-5601.824871180671</v>
+        <v>-15259.926261862</v>
       </c>
       <c r="J51" t="n">
-        <v>5611.752142523096</v>
+        <v>10052.65244557272</v>
       </c>
       <c r="K51" t="n">
-        <v>1449041.92913279</v>
+        <v>858810.3141386984</v>
       </c>
     </row>
     <row r="52">
@@ -2447,31 +2447,31 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1997</v>
+        <v>2000</v>
       </c>
       <c r="D52" t="n">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="E52" t="n">
-        <v>-306351.453753998</v>
+        <v>-105425.8731684931</v>
       </c>
       <c r="F52" t="n">
-        <v>-38072.80732296747</v>
+        <v>-23249.10878535087</v>
       </c>
       <c r="G52" t="n">
-        <v>28597.20803161</v>
+        <v>29574.37566623277</v>
       </c>
       <c r="H52" t="n">
-        <v>3134.584874412747</v>
+        <v>7174.133170232562</v>
       </c>
       <c r="I52" t="n">
-        <v>-11570.67477498793</v>
+        <v>-8981.791447433499</v>
       </c>
       <c r="J52" t="n">
-        <v>6923.251379103393</v>
+        <v>5100.594394739099</v>
       </c>
       <c r="K52" t="n">
-        <v>1142690.475378792</v>
+        <v>753384.4409702052</v>
       </c>
     </row>
     <row r="53">
@@ -2486,31 +2486,31 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="D53" t="n">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="E53" t="n">
-        <v>846829.9900844123</v>
+        <v>-370336.3087934402</v>
       </c>
       <c r="F53" t="n">
-        <v>-35891.76467357231</v>
+        <v>-53895.64025786311</v>
       </c>
       <c r="G53" t="n">
-        <v>44827.67402699932</v>
+        <v>18791.55278730535</v>
       </c>
       <c r="H53" t="n">
-        <v>18428.3261234367</v>
+        <v>3335.045344497479</v>
       </c>
       <c r="I53" t="n">
-        <v>-307.9320221484953</v>
+        <v>-9488.743281581643</v>
       </c>
       <c r="J53" t="n">
-        <v>7797.9807095253</v>
+        <v>5761.067636975771</v>
       </c>
       <c r="K53" t="n">
-        <v>1989520.465463204</v>
+        <v>383048.1321767651</v>
       </c>
     </row>
     <row r="54">
@@ -2525,31 +2525,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D54" t="n">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="E54" t="n">
-        <v>-678754.585424637</v>
+        <v>-232883.452727284</v>
       </c>
       <c r="F54" t="n">
-        <v>-73805.54731452065</v>
+        <v>-43858.86871141105</v>
       </c>
       <c r="G54" t="n">
-        <v>44013.2588697821</v>
+        <v>36722.58618486718</v>
       </c>
       <c r="H54" t="n">
-        <v>3344.369109869091</v>
+        <v>2247.496303473798</v>
       </c>
       <c r="I54" t="n">
-        <v>-15259.926261862</v>
+        <v>-6559.47914418791</v>
       </c>
       <c r="J54" t="n">
-        <v>10246.60088195523</v>
+        <v>5773.923076407891</v>
       </c>
       <c r="K54" t="n">
-        <v>1310765.880038567</v>
+        <v>150164.6794494811</v>
       </c>
     </row>
     <row r="55">
@@ -2564,31 +2564,31 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D55" t="n">
-        <v>157</v>
+        <v>246</v>
       </c>
       <c r="E55" t="n">
-        <v>-98017.92101747029</v>
+        <v>121635.8611025378</v>
       </c>
       <c r="F55" t="n">
-        <v>-23249.10878535087</v>
+        <v>-41352.99479838212</v>
       </c>
       <c r="G55" t="n">
-        <v>33379.37859662354</v>
+        <v>30489.93726952295</v>
       </c>
       <c r="H55" t="n">
-        <v>7174.133170232562</v>
+        <v>3434.931354515131</v>
       </c>
       <c r="I55" t="n">
-        <v>-8981.791447433499</v>
+        <v>-2720.304686321186</v>
       </c>
       <c r="J55" t="n">
-        <v>5323.825918833743</v>
+        <v>4589.650085830276</v>
       </c>
       <c r="K55" t="n">
-        <v>1212747.959021097</v>
+        <v>271800.5405520189</v>
       </c>
     </row>
     <row r="56">
@@ -2603,31 +2603,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="D56" t="n">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E56" t="n">
-        <v>-371914.4293373047</v>
+        <v>268905.1311276708</v>
       </c>
       <c r="F56" t="n">
-        <v>-53895.64025786311</v>
+        <v>-28820.85095177695</v>
       </c>
       <c r="G56" t="n">
-        <v>18791.55278730535</v>
+        <v>35721.88507052233</v>
       </c>
       <c r="H56" t="n">
-        <v>3335.045344497479</v>
+        <v>6078.579437875715</v>
       </c>
       <c r="I56" t="n">
-        <v>-9681.468502564943</v>
+        <v>-2587.445602139392</v>
       </c>
       <c r="J56" t="n">
-        <v>5769.281669252575</v>
+        <v>4788.059411712244</v>
       </c>
       <c r="K56" t="n">
-        <v>840833.5296837923</v>
+        <v>540705.6716796895</v>
       </c>
     </row>
     <row r="57">
@@ -2642,31 +2642,31 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="D57" t="n">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="E57" t="n">
-        <v>-232810.9350590533</v>
+        <v>89318.30161950493</v>
       </c>
       <c r="F57" t="n">
-        <v>-43858.86871141105</v>
+        <v>-30521.87485392984</v>
       </c>
       <c r="G57" t="n">
-        <v>36722.58618486718</v>
+        <v>34198.81660823461</v>
       </c>
       <c r="H57" t="n">
-        <v>2247.496303473798</v>
+        <v>4489.599459070609</v>
       </c>
       <c r="I57" t="n">
-        <v>-6559.47914418791</v>
+        <v>-3401.454279960317</v>
       </c>
       <c r="J57" t="n">
-        <v>5776.782966893292</v>
+        <v>4274.366896734628</v>
       </c>
       <c r="K57" t="n">
-        <v>608022.5946247389</v>
+        <v>630023.9732991945</v>
       </c>
     </row>
     <row r="58">
@@ -2681,31 +2681,31 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="D58" t="n">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="E58" t="n">
-        <v>122355.8192619373</v>
+        <v>809664.1204055708</v>
       </c>
       <c r="F58" t="n">
-        <v>-41352.99479838212</v>
+        <v>-11073.87368578531</v>
       </c>
       <c r="G58" t="n">
-        <v>30489.93726952295</v>
+        <v>36300.28805443111</v>
       </c>
       <c r="H58" t="n">
-        <v>3434.931354515131</v>
+        <v>13439.01835158393</v>
       </c>
       <c r="I58" t="n">
-        <v>-2720.304686321186</v>
+        <v>93.61937948179748</v>
       </c>
       <c r="J58" t="n">
-        <v>4590.805913253631</v>
+        <v>4825.380734916639</v>
       </c>
       <c r="K58" t="n">
-        <v>730378.4138866762</v>
+        <v>1439688.093704765</v>
       </c>
     </row>
     <row r="59">
@@ -2720,31 +2720,31 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="D59" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="E59" t="n">
-        <v>268780.8500474123</v>
+        <v>-1369381.612773595</v>
       </c>
       <c r="F59" t="n">
-        <v>-28820.85095177695</v>
+        <v>-56923.49265621231</v>
       </c>
       <c r="G59" t="n">
-        <v>35721.88507052233</v>
+        <v>5855.420403522891</v>
       </c>
       <c r="H59" t="n">
-        <v>6078.579437875715</v>
+        <v>-104.7114967442665</v>
       </c>
       <c r="I59" t="n">
-        <v>-2587.445602139392</v>
+        <v>-17620.48233141322</v>
       </c>
       <c r="J59" t="n">
-        <v>4793.450433177229</v>
+        <v>6259.266825638023</v>
       </c>
       <c r="K59" t="n">
-        <v>999159.2639340885</v>
+        <v>70306.48093117052</v>
       </c>
     </row>
     <row r="60">
@@ -2759,31 +2759,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="D60" t="n">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="E60" t="n">
-        <v>88822.20472635742</v>
+        <v>70287.89824111162</v>
       </c>
       <c r="F60" t="n">
-        <v>-30521.87485392984</v>
+        <v>-76028.28329657724</v>
       </c>
       <c r="G60" t="n">
-        <v>34198.81660823461</v>
+        <v>43210.10578903389</v>
       </c>
       <c r="H60" t="n">
-        <v>4489.599459070609</v>
+        <v>5448.758094732264</v>
       </c>
       <c r="I60" t="n">
-        <v>-3401.454279960317</v>
+        <v>-2907.047608462874</v>
       </c>
       <c r="J60" t="n">
-        <v>4278.799675058016</v>
+        <v>6459.326499951731</v>
       </c>
       <c r="K60" t="n">
-        <v>1087981.468660446</v>
+        <v>140594.3791722821</v>
       </c>
     </row>
     <row r="61">
@@ -2798,31 +2798,31 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="D61" t="n">
-        <v>270</v>
+        <v>313</v>
       </c>
       <c r="E61" t="n">
-        <v>812169.5644282999</v>
+        <v>-463551.5576886907</v>
       </c>
       <c r="F61" t="n">
-        <v>-11073.87368578531</v>
+        <v>-37478.31825272848</v>
       </c>
       <c r="G61" t="n">
-        <v>36300.28805443111</v>
+        <v>20791.76283861731</v>
       </c>
       <c r="H61" t="n">
-        <v>13681.62267156788</v>
+        <v>1424.653665719406</v>
       </c>
       <c r="I61" t="n">
-        <v>93.61937948179748</v>
+        <v>-6699.602314308724</v>
       </c>
       <c r="J61" t="n">
-        <v>4839.293734526867</v>
+        <v>3981.904940377663</v>
       </c>
       <c r="K61" t="n">
-        <v>1900151.033088746</v>
+        <v>-322957.1785164086</v>
       </c>
     </row>
     <row r="62">
@@ -2837,31 +2837,31 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="D62" t="n">
-        <v>280</v>
+        <v>352</v>
       </c>
       <c r="E62" t="n">
-        <v>-1375082.167883381</v>
+        <v>179279.952943622</v>
       </c>
       <c r="F62" t="n">
-        <v>-56923.49265621231</v>
+        <v>-9232.380148991095</v>
       </c>
       <c r="G62" t="n">
-        <v>5855.420403522891</v>
+        <v>30896.10465278693</v>
       </c>
       <c r="H62" t="n">
-        <v>-104.7114967442665</v>
+        <v>4330.641144393001</v>
       </c>
       <c r="I62" t="n">
-        <v>-17620.48233141322</v>
+        <v>-2758.638647475345</v>
       </c>
       <c r="J62" t="n">
-        <v>6300.168805462878</v>
+        <v>3125.648615012919</v>
       </c>
       <c r="K62" t="n">
-        <v>525068.8652053643</v>
+        <v>-143677.2255727866</v>
       </c>
     </row>
     <row r="63">
@@ -2876,31 +2876,31 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="D63" t="n">
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="E63" t="n">
-        <v>72291.99560082672</v>
+        <v>584159.000281234</v>
       </c>
       <c r="F63" t="n">
-        <v>-76028.28329657724</v>
+        <v>-22734.35225270319</v>
       </c>
       <c r="G63" t="n">
-        <v>43210.10578903389</v>
+        <v>59471.26219142057</v>
       </c>
       <c r="H63" t="n">
-        <v>5448.758094732264</v>
+        <v>7332.412714523665</v>
       </c>
       <c r="I63" t="n">
-        <v>-2907.047608462874</v>
+        <v>-894.8320510497008</v>
       </c>
       <c r="J63" t="n">
-        <v>6466.74195094938</v>
+        <v>4532.687405334225</v>
       </c>
       <c r="K63" t="n">
-        <v>597360.860806191</v>
+        <v>440481.7747084474</v>
       </c>
     </row>
     <row r="64">
@@ -2915,31 +2915,31 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="D64" t="n">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="E64" t="n">
-        <v>-464404.1884969707</v>
+        <v>-651226.8359661284</v>
       </c>
       <c r="F64" t="n">
-        <v>-37478.31825272848</v>
+        <v>-21179.87426114766</v>
       </c>
       <c r="G64" t="n">
-        <v>20791.76283861731</v>
+        <v>12066.63290840417</v>
       </c>
       <c r="H64" t="n">
-        <v>1490.881899662885</v>
+        <v>1139.062587733462</v>
       </c>
       <c r="I64" t="n">
-        <v>-6699.602314308724</v>
+        <v>-8583.470653301123</v>
       </c>
       <c r="J64" t="n">
-        <v>3986.39185272745</v>
+        <v>3377.64264318077</v>
       </c>
       <c r="K64" t="n">
-        <v>132956.6723092203</v>
+        <v>-210745.061257681</v>
       </c>
     </row>
     <row r="65">
@@ -2954,31 +2954,31 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="D65" t="n">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="E65" t="n">
-        <v>181296.3818018515</v>
+        <v>-489313.1235528758</v>
       </c>
       <c r="F65" t="n">
-        <v>-9232.380148991095</v>
+        <v>-37903.01812642963</v>
       </c>
       <c r="G65" t="n">
-        <v>30896.10465278693</v>
+        <v>5283.864448771692</v>
       </c>
       <c r="H65" t="n">
-        <v>4469.661253320715</v>
+        <v>1453.67947483475</v>
       </c>
       <c r="I65" t="n">
-        <v>-2758.638647475345</v>
+        <v>-5270.1273954958</v>
       </c>
       <c r="J65" t="n">
-        <v>3137.406914843433</v>
+        <v>4147.932145526377</v>
       </c>
       <c r="K65" t="n">
-        <v>314253.0541110717</v>
+        <v>-700058.1848105567</v>
       </c>
     </row>
     <row r="66">
@@ -2993,31 +2993,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D66" t="n">
-        <v>347</v>
+        <v>396</v>
       </c>
       <c r="E66" t="n">
-        <v>585505.5677286925</v>
+        <v>-523857.4779506734</v>
       </c>
       <c r="F66" t="n">
-        <v>-22734.35225270319</v>
+        <v>-17645.03289066887</v>
       </c>
       <c r="G66" t="n">
-        <v>59471.26219142057</v>
+        <v>19263.08920092183</v>
       </c>
       <c r="H66" t="n">
-        <v>7604.189268490673</v>
+        <v>2282.585082326452</v>
       </c>
       <c r="I66" t="n">
-        <v>-894.8320510497008</v>
+        <v>-6072.658736621514</v>
       </c>
       <c r="J66" t="n">
-        <v>4536.890438663542</v>
+        <v>3452.77629486728</v>
       </c>
       <c r="K66" t="n">
-        <v>899758.6218397643</v>
+        <v>-1223915.66276123</v>
       </c>
     </row>
     <row r="67">
@@ -3032,31 +3032,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="D67" t="n">
-        <v>345</v>
+        <v>472</v>
       </c>
       <c r="E67" t="n">
-        <v>-654026.1940813249</v>
+        <v>-417228.6145947812</v>
       </c>
       <c r="F67" t="n">
-        <v>-21179.87426114766</v>
+        <v>-57510.76229683871</v>
       </c>
       <c r="G67" t="n">
-        <v>12066.63290840417</v>
+        <v>9540.940762503549</v>
       </c>
       <c r="H67" t="n">
-        <v>1139.062587733462</v>
+        <v>2062.995559352515</v>
       </c>
       <c r="I67" t="n">
-        <v>-8583.470653301123</v>
+        <v>-4904.98219427315</v>
       </c>
       <c r="J67" t="n">
-        <v>3398.228226561483</v>
+        <v>4128.633712375087</v>
       </c>
       <c r="K67" t="n">
-        <v>245732.4277584394</v>
+        <v>-1641144.277356011</v>
       </c>
     </row>
     <row r="68">
@@ -3071,31 +3071,31 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="D68" t="n">
-        <v>374</v>
+        <v>529</v>
       </c>
       <c r="E68" t="n">
-        <v>-490317.2083251912</v>
+        <v>269586.6476210657</v>
       </c>
       <c r="F68" t="n">
-        <v>-37903.01812642963</v>
+        <v>-13822.49749399014</v>
       </c>
       <c r="G68" t="n">
-        <v>5283.864448771692</v>
+        <v>61385.99948446383</v>
       </c>
       <c r="H68" t="n">
-        <v>1453.67947483475</v>
+        <v>4049.74045472106</v>
       </c>
       <c r="I68" t="n">
-        <v>-5270.1273954958</v>
+        <v>-2269.8730773164</v>
       </c>
       <c r="J68" t="n">
-        <v>4149.94661438129</v>
+        <v>3585.771521166199</v>
       </c>
       <c r="K68" t="n">
-        <v>-244584.7805667517</v>
+        <v>-1371557.629734945</v>
       </c>
     </row>
     <row r="69">
@@ -3110,31 +3110,31 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D69" t="n">
-        <v>396</v>
+        <v>444</v>
       </c>
       <c r="E69" t="n">
-        <v>-523314.4852711426</v>
+        <v>1472509.518916817</v>
       </c>
       <c r="F69" t="n">
-        <v>-17645.03289066887</v>
+        <v>-4438.381133676447</v>
       </c>
       <c r="G69" t="n">
-        <v>19263.08920092183</v>
+        <v>42933.66624994716</v>
       </c>
       <c r="H69" t="n">
-        <v>2282.585082326452</v>
+        <v>11030.87250453827</v>
       </c>
       <c r="I69" t="n">
-        <v>-6072.658736621514</v>
+        <v>-280.4720268814872</v>
       </c>
       <c r="J69" t="n">
-        <v>3460.583546366037</v>
+        <v>4535.367533406796</v>
       </c>
       <c r="K69" t="n">
-        <v>-767899.2658378943</v>
+        <v>100951.8891818712</v>
       </c>
     </row>
     <row r="70">
@@ -3149,31 +3149,31 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="D70" t="n">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="E70" t="n">
-        <v>-417983.2133015893</v>
+        <v>-906216.0284468191</v>
       </c>
       <c r="F70" t="n">
-        <v>-57510.76229683871</v>
+        <v>-34791.07032620037</v>
       </c>
       <c r="G70" t="n">
-        <v>9540.940762503549</v>
+        <v>9880.819199281237</v>
       </c>
       <c r="H70" t="n">
-        <v>2062.995559352515</v>
+        <v>1644.35286443422</v>
       </c>
       <c r="I70" t="n">
-        <v>-4904.98219427315</v>
+        <v>-8712.485471207954</v>
       </c>
       <c r="J70" t="n">
-        <v>4130.245515695804</v>
+        <v>3803.253709170901</v>
       </c>
       <c r="K70" t="n">
-        <v>-1185882.479139484</v>
+        <v>-805264.1392649479</v>
       </c>
     </row>
     <row r="71">
@@ -3188,31 +3188,31 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D71" t="n">
-        <v>529</v>
+        <v>468</v>
       </c>
       <c r="E71" t="n">
-        <v>269659.6905625549</v>
+        <v>989379.74835616</v>
       </c>
       <c r="F71" t="n">
-        <v>-13822.49749399014</v>
+        <v>-10504.25501220978</v>
       </c>
       <c r="G71" t="n">
-        <v>61385.99948446383</v>
+        <v>30110.99628750776</v>
       </c>
       <c r="H71" t="n">
-        <v>4049.74045472106</v>
+        <v>7415.896591211917</v>
       </c>
       <c r="I71" t="n">
-        <v>-2269.8730773164</v>
+        <v>-348.7759187184498</v>
       </c>
       <c r="J71" t="n">
-        <v>3587.222879385477</v>
+        <v>3339.66777565095</v>
       </c>
       <c r="K71" t="n">
-        <v>-916222.7885769287</v>
+        <v>184115.6090912122</v>
       </c>
     </row>
     <row r="72">
@@ -3227,31 +3227,31 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D72" t="n">
-        <v>444</v>
+        <v>489</v>
       </c>
       <c r="E72" t="n">
-        <v>1473693.300737414</v>
+        <v>-1157160.819010331</v>
       </c>
       <c r="F72" t="n">
-        <v>-4438.381133676447</v>
+        <v>-40615.34963160719</v>
       </c>
       <c r="G72" t="n">
-        <v>42933.66624994716</v>
+        <v>10300.28889546782</v>
       </c>
       <c r="H72" t="n">
-        <v>11030.87250453827</v>
+        <v>457.0144336857608</v>
       </c>
       <c r="I72" t="n">
-        <v>-280.4720268814872</v>
+        <v>-8811.569380182224</v>
       </c>
       <c r="J72" t="n">
-        <v>4537.178574939734</v>
+        <v>4028.896953354159</v>
       </c>
       <c r="K72" t="n">
-        <v>557470.5121604854</v>
+        <v>-973045.2099191184</v>
       </c>
     </row>
     <row r="73">
@@ -3266,31 +3266,31 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="D73" t="n">
-        <v>427</v>
+        <v>588</v>
       </c>
       <c r="E73" t="n">
-        <v>-907607.6446493583</v>
+        <v>-857530.074031821</v>
       </c>
       <c r="F73" t="n">
-        <v>-34791.07032620037</v>
+        <v>-20963.56863713968</v>
       </c>
       <c r="G73" t="n">
-        <v>9880.819199281237</v>
+        <v>12801.85498280777</v>
       </c>
       <c r="H73" t="n">
-        <v>1644.35286443422</v>
+        <v>608.017523628909</v>
       </c>
       <c r="I73" t="n">
-        <v>-8712.485471207954</v>
+        <v>-6412.808157372411</v>
       </c>
       <c r="J73" t="n">
-        <v>3806.456364988715</v>
+        <v>2775.494746896878</v>
       </c>
       <c r="K73" t="n">
-        <v>-350137.132488873</v>
+        <v>-1830575.283950939</v>
       </c>
     </row>
     <row r="74">
@@ -3305,31 +3305,31 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D74" t="n">
-        <v>468</v>
+        <v>589</v>
       </c>
       <c r="E74" t="n">
-        <v>994806.7785628414</v>
+        <v>-851137.9964508961</v>
       </c>
       <c r="F74" t="n">
-        <v>-10504.25501220978</v>
+        <v>-49188.56203779345</v>
       </c>
       <c r="G74" t="n">
-        <v>30110.99628750776</v>
+        <v>37788.90313583307</v>
       </c>
       <c r="H74" t="n">
-        <v>7415.896591211917</v>
+        <v>951.4006325558884</v>
       </c>
       <c r="I74" t="n">
-        <v>-348.7759187184498</v>
+        <v>-7135.863792850691</v>
       </c>
       <c r="J74" t="n">
-        <v>3362.405960064152</v>
+        <v>4401.058406984516</v>
       </c>
       <c r="K74" t="n">
-        <v>644669.6460739684</v>
+        <v>-2681713.280401835</v>
       </c>
     </row>
     <row r="75">
@@ -3344,31 +3344,31 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="D75" t="n">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="E75" t="n">
-        <v>-1161653.306086019</v>
+        <v>1286879.417348155</v>
       </c>
       <c r="F75" t="n">
-        <v>-40615.34963160719</v>
+        <v>-9175.895423955399</v>
       </c>
       <c r="G75" t="n">
-        <v>10300.28889546782</v>
+        <v>43931.88218087849</v>
       </c>
       <c r="H75" t="n">
-        <v>457.0144336857608</v>
+        <v>12009.99593846041</v>
       </c>
       <c r="I75" t="n">
-        <v>-9070.008563919057</v>
+        <v>-905.0016021454828</v>
       </c>
       <c r="J75" t="n">
-        <v>4037.370089676545</v>
+        <v>5651.508868805652</v>
       </c>
       <c r="K75" t="n">
-        <v>-516983.660012051</v>
+        <v>-1394833.86305368</v>
       </c>
     </row>
     <row r="76">
@@ -3383,31 +3383,31 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D76" t="n">
-        <v>588</v>
+        <v>395</v>
       </c>
       <c r="E76" t="n">
-        <v>-860572.116675097</v>
+        <v>562188.4791085804</v>
       </c>
       <c r="F76" t="n">
-        <v>-20963.56863713968</v>
+        <v>-33717.30052944132</v>
       </c>
       <c r="G76" t="n">
-        <v>12801.85498280777</v>
+        <v>19630.2594684148</v>
       </c>
       <c r="H76" t="n">
-        <v>608.017523628909</v>
+        <v>5984.017135397677</v>
       </c>
       <c r="I76" t="n">
-        <v>-6412.808157372411</v>
+        <v>-920.0237039105448</v>
       </c>
       <c r="J76" t="n">
-        <v>2788.038014674264</v>
+        <v>3243.273680778309</v>
       </c>
       <c r="K76" t="n">
-        <v>-1377555.776687148</v>
+        <v>-832645.3839450998</v>
       </c>
     </row>
     <row r="77">
@@ -3422,148 +3422,31 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D77" t="n">
-        <v>589</v>
+        <v>392</v>
       </c>
       <c r="E77" t="n">
-        <v>-850306.7011893077</v>
+        <v>232979.6974244362</v>
       </c>
       <c r="F77" t="n">
-        <v>-49188.56203779345</v>
+        <v>-30456.72260170012</v>
       </c>
       <c r="G77" t="n">
-        <v>37788.90313583307</v>
+        <v>14846.10817859102</v>
       </c>
       <c r="H77" t="n">
-        <v>951.4006325558884</v>
+        <v>3184.575914656525</v>
       </c>
       <c r="I77" t="n">
-        <v>-7135.863792850691</v>
+        <v>-1370.300203902185</v>
       </c>
       <c r="J77" t="n">
-        <v>4406.34192116673</v>
+        <v>2369.41505800979</v>
       </c>
       <c r="K77" t="n">
-        <v>-2227862.477876456</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D78" t="n">
-        <v>452</v>
-      </c>
-      <c r="E78" t="n">
-        <v>1291389.884542461</v>
-      </c>
-      <c r="F78" t="n">
-        <v>-9175.895423955399</v>
-      </c>
-      <c r="G78" t="n">
-        <v>43931.88218087849</v>
-      </c>
-      <c r="H78" t="n">
-        <v>12009.99593846041</v>
-      </c>
-      <c r="I78" t="n">
-        <v>-905.0016021454828</v>
-      </c>
-      <c r="J78" t="n">
-        <v>5655.162946130042</v>
-      </c>
-      <c r="K78" t="n">
-        <v>-936472.5933339943</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D79" t="n">
-        <v>395</v>
-      </c>
-      <c r="E79" t="n">
-        <v>563901.1531769885</v>
-      </c>
-      <c r="F79" t="n">
-        <v>-33717.30052944132</v>
-      </c>
-      <c r="G79" t="n">
-        <v>19630.2594684148</v>
-      </c>
-      <c r="H79" t="n">
-        <v>5984.017135397677</v>
-      </c>
-      <c r="I79" t="n">
-        <v>-920.0237039105448</v>
-      </c>
-      <c r="J79" t="n">
-        <v>3245.098743352239</v>
-      </c>
-      <c r="K79" t="n">
-        <v>-372571.4401570058</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D80" t="n">
-        <v>392</v>
-      </c>
-      <c r="E80" t="n">
-        <v>232969.7649355713</v>
-      </c>
-      <c r="F80" t="n">
-        <v>-30456.72260170012</v>
-      </c>
-      <c r="G80" t="n">
-        <v>14846.10817859102</v>
-      </c>
-      <c r="H80" t="n">
-        <v>3184.575914656525</v>
-      </c>
-      <c r="I80" t="n">
-        <v>-1370.300203902185</v>
-      </c>
-      <c r="J80" t="n">
-        <v>2373.444985469924</v>
-      </c>
-      <c r="K80" t="n">
-        <v>-139601.6752214345</v>
+        <v>-599665.6865206636</v>
       </c>
     </row>
   </sheetData>
